--- a/assets/YRA2026_List_of_abstracts.xlsx
+++ b/assets/YRA2026_List_of_abstracts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/880d6438edbec6ad/Documents/YRA Conference/YRA2026/Abstract Book/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/880d6438edbec6ad/Documents/YRA Conference/yrarch.github.io/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_30B787AD558C25A241A2D776B67318DFFC0BE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67897913-AFEC-4A53-97B3-A483041952DF}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_30B787AD558C25A241A2D776B67318DFFC0BE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA170386-C922-480C-A769-FCD8DBD43EC8}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,10 +220,6 @@
     <t>Zooarchaeology, Enamel carbonate analysis, Interdisciplinary study, Paleoenvironment reconstruction</t>
   </si>
   <si>
-    <t>Montlleó is an open-air archaeological site in the Pyrenees (Catalonia,
-Spain) seasonally occupied by hunter-gatherers during and after the Last Glacial Maximum (LGM), with strategic access to a wide variety of ecosystems. During this last glacial stage, the Pyrenean area underwent alternating extreme cold and temperate conditions, leading to the contraction and expansion of grassy steppes and deciduous forests. Montlleó contains layers dating to the LGM, including the Upper Solutrean and Badegoulian (23000 – 20000 cal BP) and just after the LGM, in the Lower Magdalenian (19500 – 17500 cal BP). At Montlleó, wild horses (Equus ferus) represent most of the large herbivores hunted by people. Their tooth enamel can be sampled in small parallel lines along the crown axis to track changes in δ¹³C and δ¹⁸O values across incremental tooth formation. These isotope values are respectively influenced by the animal’s diet and water intake, which can show seasonal trends. This study uses a multi-layer isotopic analysis complemented by microwear analysis, which reflects the last weeks of dietary history, to infer the environmental behavior of E. ferus at Montlleó. This provides further insights into the surrounding environments and habitats exploited by humans during and after the LGM in a mountainous context.</t>
-  </si>
-  <si>
     <t>Jett Liska</t>
   </si>
   <si>
@@ -980,6 +976,9 @@
   </si>
   <si>
     <t>Order</t>
+  </si>
+  <si>
+    <t>Montlleó is an open-air archaeological site in the Pyrenees (Catalonia, Spain) seasonally occupied by hunter-gatherers during and after the Last Glacial Maximum (LGM), with strategic access to a wide variety of ecosystems. During this last glacial stage, the Pyrenean area underwent alternating extreme cold and temperate conditions, leading to the contraction and expansion of grassy steppes and deciduous forests. Montlleó contains layers dating to the LGM, including the Upper Solutrean and Badegoulian (23000 – 20000 cal BP) and just after the LGM, in the Lower Magdalenian (19500 – 17500 cal BP). At Montlleó, wild horses (Equus ferus) represent most of the large herbivores hunted by people. Their tooth enamel can be sampled in small parallel lines along the crown axis to track changes in δ¹³C and δ¹⁸O values across incremental tooth formation. These isotope values are respectively influenced by the animal’s diet and water intake, which can show seasonal trends. This study uses a multi-layer isotopic analysis complemented by microwear analysis, which reflects the last weeks of dietary history, to infer the environmental behavior of E. ferus at Montlleó. This provides further insights into the surrounding environments and habitats exploited by humans during and after the LGM in a mountainous context.</t>
   </si>
 </sst>
 </file>
@@ -1021,11 +1020,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1042,10 +1044,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1377,10 +1375,10 @@
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1523,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1568,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R2" t="s">
         <v>24</v>
@@ -1594,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
@@ -1626,7 +1624,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -1644,7 +1642,7 @@
         <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
@@ -1656,18 +1654,18 @@
         <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -1675,7 +1673,7 @@
       <c r="D5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F5" t="s">
@@ -1747,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
@@ -1765,7 +1763,7 @@
         <v>54</v>
       </c>
       <c r="H6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I6" t="s">
         <v>55</v>
@@ -1798,7 +1796,7 @@
         <v>59</v>
       </c>
       <c r="U6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="V6" t="s">
         <v>60</v>
@@ -1812,7 +1810,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
         <v>61</v>
@@ -1821,19 +1819,19 @@
         <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
       </c>
       <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I7" t="s">
         <v>64</v>
-      </c>
-      <c r="H7" t="s">
-        <v>294</v>
-      </c>
-      <c r="I7" t="s">
-        <v>65</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1845,7 +1843,7 @@
         <v>20</v>
       </c>
       <c r="M7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
@@ -1854,49 +1852,49 @@
         <v>19</v>
       </c>
       <c r="P7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>298</v>
+      </c>
+      <c r="R7" t="s">
         <v>66</v>
       </c>
-      <c r="Q7" t="s">
-        <v>299</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T7" t="s">
         <v>67</v>
       </c>
-      <c r="S7" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>68</v>
       </c>
-      <c r="U7" t="s">
+      <c r="W7" t="s">
+        <v>19</v>
+      </c>
+      <c r="X7" t="s">
         <v>69</v>
       </c>
-      <c r="W7" t="s">
-        <v>19</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
+        <v>292</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB7" t="s">
         <v>70</v>
       </c>
-      <c r="Y7" t="s">
-        <v>293</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
+        <v>292</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG7" t="s">
         <v>71</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>293</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>72</v>
       </c>
       <c r="AI7" t="s">
         <v>18</v>
@@ -1907,28 +1905,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>76</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
         <v>77</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>78</v>
-      </c>
-      <c r="I8" t="s">
-        <v>79</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -1942,25 +1940,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
         <v>80</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>82</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" t="s">
         <v>83</v>
-      </c>
-      <c r="H9" t="s">
-        <v>84</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -1974,76 +1972,76 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
         <v>85</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>87</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" t="s">
         <v>88</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
         <v>89</v>
       </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" t="s">
         <v>90</v>
       </c>
-      <c r="M10" t="s">
-        <v>89</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" t="s">
         <v>91</v>
       </c>
-      <c r="O10" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" t="s">
         <v>92</v>
       </c>
-      <c r="Q10" t="s">
-        <v>89</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" t="s">
         <v>93</v>
       </c>
-      <c r="S10" t="s">
-        <v>19</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
+        <v>88</v>
+      </c>
+      <c r="V10" t="s">
         <v>94</v>
       </c>
-      <c r="U10" t="s">
-        <v>89</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
+        <v>19</v>
+      </c>
+      <c r="X10" t="s">
         <v>95</v>
       </c>
-      <c r="W10" t="s">
-        <v>19</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
         <v>96</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Z10" t="s">
         <v>97</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>98</v>
       </c>
       <c r="AA10" t="s">
         <v>18</v>
@@ -2054,88 +2052,88 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
         <v>99</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>101</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" t="s">
         <v>102</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>103</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" t="s">
         <v>104</v>
       </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" t="s">
-        <v>90</v>
-      </c>
-      <c r="M11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N11" t="s">
-        <v>91</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>105</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>106</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" t="s">
         <v>107</v>
       </c>
-      <c r="S11" t="s">
-        <v>19</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>108</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>109</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
+        <v>19</v>
+      </c>
+      <c r="X11" t="s">
         <v>110</v>
       </c>
-      <c r="W11" t="s">
-        <v>19</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
         <v>111</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AA11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB11" t="s">
         <v>112</v>
       </c>
-      <c r="AA11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>113</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>114</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>115</v>
       </c>
       <c r="AE11" t="s">
         <v>18</v>
@@ -2146,25 +2144,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" t="s">
         <v>116</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>117</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>118</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>119</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>120</v>
-      </c>
-      <c r="H12" t="s">
-        <v>121</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -2178,91 +2176,91 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
         <v>122</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>123</v>
-      </c>
-      <c r="E13" t="s">
-        <v>124</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" t="s">
+        <v>301</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" t="s">
+        <v>302</v>
+      </c>
+      <c r="O13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>128</v>
+      </c>
+      <c r="S13" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s">
+        <v>129</v>
+      </c>
+      <c r="U13" t="s">
+        <v>130</v>
+      </c>
+      <c r="W13" t="s">
+        <v>19</v>
+      </c>
+      <c r="X13" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK13" t="s">
         <v>125</v>
-      </c>
-      <c r="H13" t="s">
-        <v>302</v>
-      </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" t="s">
-        <v>127</v>
-      </c>
-      <c r="M13" t="s">
-        <v>303</v>
-      </c>
-      <c r="O13" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>129</v>
-      </c>
-      <c r="S13" t="s">
-        <v>19</v>
-      </c>
-      <c r="T13" t="s">
-        <v>130</v>
-      </c>
-      <c r="U13" t="s">
-        <v>131</v>
-      </c>
-      <c r="W13" t="s">
-        <v>19</v>
-      </c>
-      <c r="X13" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>136</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>126</v>
       </c>
       <c r="AM13" t="s">
         <v>18</v>
@@ -2273,79 +2271,79 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" t="s">
         <v>139</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>140</v>
-      </c>
-      <c r="E14" t="s">
-        <v>141</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" t="s">
         <v>142</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>143</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" t="s">
         <v>144</v>
       </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>145</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>146</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P14" t="s">
         <v>147</v>
       </c>
-      <c r="O14" t="s">
-        <v>19</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>145</v>
+      </c>
+      <c r="R14" t="s">
         <v>148</v>
       </c>
-      <c r="Q14" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s">
         <v>149</v>
       </c>
-      <c r="S14" t="s">
-        <v>19</v>
-      </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
+        <v>145</v>
+      </c>
+      <c r="V14" t="s">
         <v>150</v>
       </c>
-      <c r="U14" t="s">
-        <v>146</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
+        <v>19</v>
+      </c>
+      <c r="X14" t="s">
         <v>151</v>
       </c>
-      <c r="W14" t="s">
-        <v>19</v>
-      </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>152</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
         <v>153</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>154</v>
       </c>
       <c r="AA14" t="s">
         <v>18</v>
@@ -2356,43 +2354,43 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" t="s">
         <v>156</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>157</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
         <v>158</v>
       </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>159</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>160</v>
-      </c>
-      <c r="N15" t="s">
-        <v>161</v>
       </c>
       <c r="O15" t="s">
         <v>18</v>
@@ -2403,25 +2401,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" t="s">
         <v>162</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>163</v>
-      </c>
-      <c r="E16" t="s">
-        <v>164</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" t="s">
         <v>165</v>
-      </c>
-      <c r="H16" t="s">
-        <v>166</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -2435,61 +2433,61 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" t="s">
         <v>167</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>168</v>
-      </c>
-      <c r="E17" t="s">
-        <v>169</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H17" t="s">
         <v>170</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>171</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" t="s">
         <v>172</v>
       </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
+        <v>170</v>
+      </c>
+      <c r="O17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P17" t="s">
         <v>173</v>
       </c>
-      <c r="M17" t="s">
-        <v>171</v>
-      </c>
-      <c r="O17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
+        <v>170</v>
+      </c>
+      <c r="S17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s">
         <v>174</v>
       </c>
-      <c r="Q17" t="s">
-        <v>171</v>
-      </c>
-      <c r="S17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
+        <v>170</v>
+      </c>
+      <c r="V17" t="s">
         <v>175</v>
-      </c>
-      <c r="U17" t="s">
-        <v>171</v>
-      </c>
-      <c r="V17" t="s">
-        <v>176</v>
       </c>
       <c r="W17" t="s">
         <v>18</v>
@@ -2500,28 +2498,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" t="s">
         <v>177</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>178</v>
-      </c>
-      <c r="E18" t="s">
-        <v>179</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
+        <v>179</v>
+      </c>
+      <c r="H18" t="s">
         <v>180</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>181</v>
-      </c>
-      <c r="I18" t="s">
-        <v>182</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -2535,28 +2533,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" t="s">
         <v>183</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>184</v>
-      </c>
-      <c r="E19" t="s">
-        <v>185</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" t="s">
+        <v>305</v>
+      </c>
+      <c r="I19" t="s">
         <v>186</v>
-      </c>
-      <c r="H19" t="s">
-        <v>306</v>
-      </c>
-      <c r="I19" t="s">
-        <v>187</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -2570,25 +2568,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" t="s">
         <v>188</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>189</v>
-      </c>
-      <c r="E20" t="s">
-        <v>190</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J20" t="s">
         <v>18</v>
@@ -2602,28 +2600,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" t="s">
         <v>192</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>193</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>194</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>195</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>297</v>
+      </c>
+      <c r="I21" t="s">
         <v>196</v>
-      </c>
-      <c r="H21" t="s">
-        <v>298</v>
-      </c>
-      <c r="I21" t="s">
-        <v>197</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -2637,61 +2635,61 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" t="s">
         <v>198</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>199</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" t="s">
         <v>200</v>
       </c>
-      <c r="F22" t="s">
-        <v>195</v>
-      </c>
-      <c r="G22" t="s">
-        <v>201</v>
-      </c>
       <c r="H22" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" t="s">
+        <v>169</v>
+      </c>
+      <c r="M22" t="s">
+        <v>170</v>
+      </c>
+      <c r="N22" t="s">
         <v>171</v>
       </c>
-      <c r="J22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="O22" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>173</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" t="s">
+        <v>174</v>
+      </c>
+      <c r="U22" t="s">
         <v>170</v>
       </c>
-      <c r="M22" t="s">
-        <v>171</v>
-      </c>
-      <c r="N22" t="s">
-        <v>172</v>
-      </c>
-      <c r="O22" t="s">
-        <v>19</v>
-      </c>
-      <c r="P22" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>174</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="V22" t="s">
         <v>175</v>
-      </c>
-      <c r="U22" t="s">
-        <v>171</v>
-      </c>
-      <c r="V22" t="s">
-        <v>176</v>
       </c>
       <c r="W22" t="s">
         <v>18</v>
@@ -2702,25 +2700,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" t="s">
         <v>202</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>203</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>194</v>
+      </c>
+      <c r="G23" t="s">
         <v>204</v>
       </c>
-      <c r="F23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>205</v>
-      </c>
-      <c r="H23" t="s">
-        <v>206</v>
       </c>
       <c r="J23" t="s">
         <v>18</v>
@@ -2734,100 +2732,100 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C24" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" t="s">
         <v>207</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>208</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>209</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" t="s">
+        <v>301</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" t="s">
         <v>210</v>
       </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="M24" t="s">
+        <v>301</v>
+      </c>
+      <c r="O24" t="s">
+        <v>19</v>
+      </c>
+      <c r="P24" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q24" t="s">
         <v>302</v>
       </c>
-      <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>137</v>
+      </c>
+      <c r="U24" t="s">
+        <v>301</v>
+      </c>
+      <c r="W24" t="s">
+        <v>19</v>
+      </c>
+      <c r="X24" t="s">
         <v>211</v>
       </c>
-      <c r="M24" t="s">
-        <v>302</v>
-      </c>
-      <c r="O24" t="s">
-        <v>19</v>
-      </c>
-      <c r="P24" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q24" t="s">
+      <c r="Y24" t="s">
         <v>303</v>
       </c>
-      <c r="S24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T24" t="s">
-        <v>138</v>
-      </c>
-      <c r="U24" t="s">
-        <v>302</v>
-      </c>
-      <c r="W24" t="s">
-        <v>19</v>
-      </c>
-      <c r="X24" t="s">
+      <c r="AA24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB24" t="s">
         <v>212</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AC24" t="s">
+        <v>303</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG24" t="s">
         <v>304</v>
       </c>
-      <c r="AA24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>213</v>
-      </c>
-      <c r="AC24" t="s">
+      <c r="AI24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK24" t="s">
         <v>304</v>
       </c>
-      <c r="AE24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>214</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>305</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ24" t="s">
+      <c r="AM24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN24" t="s">
         <v>215</v>
       </c>
-      <c r="AK24" t="s">
-        <v>305</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>216</v>
-      </c>
       <c r="AO24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AQ24" t="s">
         <v>18</v>
@@ -2850,16 +2848,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2870,7 +2868,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -2881,10 +2879,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>28</v>
@@ -2898,7 +2896,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
@@ -2909,10 +2907,10 @@
         <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
@@ -2926,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>34</v>
@@ -2940,7 +2938,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>39</v>
@@ -2954,7 +2952,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>52</v>
@@ -2962,13 +2960,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>61</v>
@@ -2976,13 +2974,13 @@
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>62</v>
@@ -2990,217 +2988,217 @@
     </row>
     <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
@@ -3214,35 +3212,35 @@
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>0</v>
@@ -3256,21 +3254,21 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>0</v>
@@ -3284,35 +3282,35 @@
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>0</v>
@@ -3326,35 +3324,35 @@
     </row>
     <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>0</v>
@@ -3368,35 +3366,35 @@
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>0</v>
@@ -3410,21 +3408,21 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>0</v>
@@ -3436,21 +3434,21 @@
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>0</v>
@@ -3464,21 +3462,21 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>0</v>
@@ -3492,59 +3490,59 @@
     </row>
     <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>0</v>
@@ -3553,24 +3551,24 @@
         <v>21</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>0</v>
@@ -3579,36 +3577,36 @@
         <v>15</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>0</v>
@@ -3617,24 +3615,24 @@
         <v>16</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>0</v>
@@ -3643,24 +3641,24 @@
         <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>0</v>
@@ -3669,7 +3667,7 @@
         <v>24</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/assets/YRA2026_List_of_abstracts.xlsx
+++ b/assets/YRA2026_List_of_abstracts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/880d6438edbec6ad/Documents/YRA Conference/yrarch.github.io/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_30B787AD558C25A241A2D776B67318DFFC0BE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA170386-C922-480C-A769-FCD8DBD43EC8}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_30B787AD558C25A241A2D776B67318DFFC0BE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{430B3A93-42C6-49F0-A18D-72FF86CB4076}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="317">
   <si>
     <t>Program order</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>ORCID iD</t>
-  </si>
-  <si>
-    <t>Do you need an invitation letter to apply for a visa?</t>
   </si>
   <si>
     <t>Add another author</t>
@@ -979,6 +976,27 @@
   </si>
   <si>
     <t>Montlleó is an open-air archaeological site in the Pyrenees (Catalonia, Spain) seasonally occupied by hunter-gatherers during and after the Last Glacial Maximum (LGM), with strategic access to a wide variety of ecosystems. During this last glacial stage, the Pyrenean area underwent alternating extreme cold and temperate conditions, leading to the contraction and expansion of grassy steppes and deciduous forests. Montlleó contains layers dating to the LGM, including the Upper Solutrean and Badegoulian (23000 – 20000 cal BP) and just after the LGM, in the Lower Magdalenian (19500 – 17500 cal BP). At Montlleó, wild horses (Equus ferus) represent most of the large herbivores hunted by people. Their tooth enamel can be sampled in small parallel lines along the crown axis to track changes in δ¹³C and δ¹⁸O values across incremental tooth formation. These isotope values are respectively influenced by the animal’s diet and water intake, which can show seasonal trends. This study uses a multi-layer isotopic analysis complemented by microwear analysis, which reflects the last weeks of dietary history, to infer the environmental behavior of E. ferus at Montlleó. This provides further insights into the surrounding environments and habitats exploited by humans during and after the LGM in a mountainous context.</t>
+  </si>
+  <si>
+    <t>n.parnetti@student.unisi.it</t>
+  </si>
+  <si>
+    <t>Multidisciplinary pXRF research in the Campiglia Marittima mining district (Tuscany, Italy): reconstructing the diachronic production history of the Madonna di Fucinaia site</t>
+  </si>
+  <si>
+    <t>This study presents a diachronic reconstruction of the Madonna di Fucinaia site (Tuscany, Italy), analyzed within the productive context of the Capattoli Valley. As part of the MINERS project (Bianchi et al. 2024), the research investigates the pre-industrial productive landscape, a central theme of the University of Siena’s investigations since the 1980s. The primary objective is a critical re-evaluation of the site's archaeometallurgical evidence by integrating archival and bibliographical source systems and historical cartography in georeferences ambient with a systematic geochemical survey via pXRF. This investigation resolves the interpretative uncertainties surrounding this multi-stratified site, outlining a complex chronological sequence (8th century BCE – mid-16th century CE) characterized by shifting functions: from a potential settlement to a funerary area, and subsequently to a metal-productive site. Notably, the new pXRF data, cross-referenced with XRF and ICP-MS data from the copper slag deposits</t>
+  </si>
+  <si>
+    <t>Archaeometallurgy, pXRF, Diachrony</t>
+  </si>
+  <si>
+    <t>Niccolò Parnetti</t>
+  </si>
+  <si>
+    <t>Department of History Sciences and Cultural Heritage, University of Siena, Siena, Italy</t>
+  </si>
+  <si>
+    <t>0009-0000-1633-5719</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1029,6 +1047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1044,6 +1063,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU24"/>
+  <dimension ref="A1:AT25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.6640625" customWidth="1"/>
@@ -1373,12 +1396,12 @@
     <col min="7" max="7" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1405,144 +1428,141 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" t="s">
-        <v>5</v>
-      </c>
-      <c r="U1" t="s">
-        <v>6</v>
-      </c>
-      <c r="V1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>9</v>
-      </c>
-      <c r="X1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -1557,22 +1577,22 @@
         <v>21</v>
       </c>
       <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>22</v>
       </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
       <c r="P2" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q2" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" t="s">
-        <v>300</v>
-      </c>
       <c r="R2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" t="s">
         <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>19</v>
       </c>
       <c r="T2" t="s">
         <v>25</v>
@@ -1581,458 +1601,434 @@
         <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>31</v>
       </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
       <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>294</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
         <v>36</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4" t="s">
         <v>295</v>
       </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" t="s">
-        <v>296</v>
-      </c>
-      <c r="O4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:46" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
         <v>42</v>
       </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
       <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
         <v>43</v>
       </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
       <c r="N5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" t="s">
         <v>44</v>
-      </c>
-      <c r="O5" t="s">
-        <v>19</v>
       </c>
       <c r="P5" t="s">
         <v>45</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" t="s">
         <v>46</v>
-      </c>
-      <c r="S5" t="s">
-        <v>19</v>
       </c>
       <c r="T5" t="s">
         <v>47</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" t="s">
         <v>48</v>
       </c>
-      <c r="W5" t="s">
-        <v>19</v>
-      </c>
       <c r="X5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" t="s">
         <v>49</v>
       </c>
-      <c r="Y5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>19</v>
-      </c>
       <c r="AB5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
         <v>53</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I6" t="s">
         <v>54</v>
       </c>
-      <c r="H6" t="s">
-        <v>294</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
         <v>55</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
       </c>
       <c r="L6" t="s">
         <v>56</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
         <v>57</v>
       </c>
-      <c r="O6" t="s">
-        <v>19</v>
-      </c>
       <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" t="s">
-        <v>19</v>
-      </c>
       <c r="T6" t="s">
+        <v>293</v>
+      </c>
+      <c r="U6" t="s">
         <v>59</v>
       </c>
-      <c r="U6" t="s">
-        <v>294</v>
-      </c>
       <c r="V6" t="s">
-        <v>60</v>
-      </c>
-      <c r="W6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
         <v>61</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" t="s">
-        <v>310</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>292</v>
+      </c>
+      <c r="I7" t="s">
         <v>63</v>
       </c>
-      <c r="H7" t="s">
-        <v>293</v>
-      </c>
-      <c r="I7" t="s">
-        <v>64</v>
-      </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
         <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="M7" t="s">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="P7" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q7" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" t="s">
-        <v>298</v>
-      </c>
       <c r="R7" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" t="s">
         <v>66</v>
-      </c>
-      <c r="S7" t="s">
-        <v>19</v>
       </c>
       <c r="T7" t="s">
         <v>67</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" t="s">
         <v>68</v>
       </c>
-      <c r="W7" t="s">
-        <v>19</v>
-      </c>
       <c r="X7" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" t="s">
         <v>69</v>
       </c>
-      <c r="Y7" t="s">
-        <v>292</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>19</v>
-      </c>
       <c r="AB7" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF7" t="s">
         <v>70</v>
       </c>
-      <c r="AC7" t="s">
-        <v>292</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AH7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
         <v>73</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>74</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>76</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>77</v>
       </c>
-      <c r="I8" t="s">
-        <v>78</v>
-      </c>
       <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
         <v>79</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>80</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
         <v>81</v>
       </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>82</v>
       </c>
-      <c r="H9" t="s">
-        <v>83</v>
-      </c>
       <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>85</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
         <v>86</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>87</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
         <v>88</v>
       </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
       <c r="L10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" t="s">
         <v>89</v>
       </c>
-      <c r="M10" t="s">
-        <v>88</v>
-      </c>
       <c r="N10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
         <v>90</v>
       </c>
-      <c r="O10" t="s">
-        <v>19</v>
-      </c>
       <c r="P10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="s">
         <v>91</v>
       </c>
-      <c r="Q10" t="s">
-        <v>88</v>
-      </c>
       <c r="R10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" t="s">
         <v>92</v>
       </c>
-      <c r="S10" t="s">
-        <v>19</v>
-      </c>
       <c r="T10" t="s">
+        <v>87</v>
+      </c>
+      <c r="U10" t="s">
         <v>93</v>
       </c>
-      <c r="U10" t="s">
-        <v>88</v>
-      </c>
       <c r="V10" t="s">
+        <v>18</v>
+      </c>
+      <c r="W10" t="s">
         <v>94</v>
-      </c>
-      <c r="W10" t="s">
-        <v>19</v>
       </c>
       <c r="X10" t="s">
         <v>95</v>
@@ -2041,57 +2037,54 @@
         <v>96</v>
       </c>
       <c r="Z10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
         <v>98</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>99</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
         <v>100</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>102</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" t="s">
+        <v>101</v>
+      </c>
+      <c r="M11" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
         <v>103</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M11" t="s">
-        <v>102</v>
-      </c>
-      <c r="N11" t="s">
-        <v>90</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
       </c>
       <c r="P11" t="s">
         <v>104</v>
@@ -2100,10 +2093,10 @@
         <v>105</v>
       </c>
       <c r="R11" t="s">
+        <v>18</v>
+      </c>
+      <c r="S11" t="s">
         <v>106</v>
-      </c>
-      <c r="S11" t="s">
-        <v>19</v>
       </c>
       <c r="T11" t="s">
         <v>107</v>
@@ -2112,19 +2105,19 @@
         <v>108</v>
       </c>
       <c r="V11" t="s">
+        <v>18</v>
+      </c>
+      <c r="W11" t="s">
         <v>109</v>
-      </c>
-      <c r="W11" t="s">
-        <v>19</v>
       </c>
       <c r="X11" t="s">
         <v>110</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA11" t="s">
         <v>111</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>19</v>
       </c>
       <c r="AB11" t="s">
         <v>112</v>
@@ -2133,172 +2126,163 @@
         <v>113</v>
       </c>
       <c r="AD11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
         <v>115</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>116</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>117</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>118</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>119</v>
       </c>
-      <c r="H12" t="s">
-        <v>120</v>
-      </c>
       <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" t="s">
         <v>121</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>122</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
         <v>123</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>124</v>
-      </c>
       <c r="H13" t="s">
+        <v>300</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" t="s">
         <v>301</v>
       </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
         <v>126</v>
-      </c>
-      <c r="M13" t="s">
-        <v>302</v>
-      </c>
-      <c r="O13" t="s">
-        <v>19</v>
       </c>
       <c r="P13" t="s">
         <v>127</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S13" t="s">
         <v>128</v>
-      </c>
-      <c r="S13" t="s">
-        <v>19</v>
       </c>
       <c r="T13" t="s">
         <v>129</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
+        <v>18</v>
+      </c>
+      <c r="W13" t="s">
         <v>130</v>
-      </c>
-      <c r="W13" t="s">
-        <v>19</v>
       </c>
       <c r="X13" t="s">
         <v>131</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA13" t="s">
         <v>132</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>19</v>
       </c>
       <c r="AB13" t="s">
         <v>133</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="s">
         <v>134</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>19</v>
       </c>
       <c r="AF13" t="s">
         <v>135</v>
       </c>
-      <c r="AG13" t="s">
+      <c r="AH13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI13" t="s">
         <v>136</v>
       </c>
-      <c r="AI13" t="s">
-        <v>19</v>
-      </c>
       <c r="AJ13" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" t="s">
         <v>138</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>139</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
         <v>140</v>
       </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>141</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>142</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
         <v>143</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
       </c>
       <c r="L14" t="s">
         <v>144</v>
@@ -2307,34 +2291,34 @@
         <v>145</v>
       </c>
       <c r="N14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
         <v>146</v>
       </c>
-      <c r="O14" t="s">
-        <v>19</v>
-      </c>
       <c r="P14" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" t="s">
         <v>147</v>
       </c>
-      <c r="Q14" t="s">
-        <v>145</v>
-      </c>
       <c r="R14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S14" t="s">
         <v>148</v>
       </c>
-      <c r="S14" t="s">
-        <v>19</v>
-      </c>
       <c r="T14" t="s">
+        <v>144</v>
+      </c>
+      <c r="U14" t="s">
         <v>149</v>
       </c>
-      <c r="U14" t="s">
-        <v>145</v>
-      </c>
       <c r="V14" t="s">
+        <v>18</v>
+      </c>
+      <c r="W14" t="s">
         <v>150</v>
-      </c>
-      <c r="W14" t="s">
-        <v>19</v>
       </c>
       <c r="X14" t="s">
         <v>151</v>
@@ -2343,45 +2327,42 @@
         <v>152</v>
       </c>
       <c r="Z14" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>306</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
         <v>154</v>
       </c>
-      <c r="E15" t="s">
-        <v>307</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>155</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>156</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
         <v>157</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
       </c>
       <c r="L15" t="s">
         <v>158</v>
@@ -2390,276 +2371,255 @@
         <v>159</v>
       </c>
       <c r="N15" t="s">
-        <v>160</v>
-      </c>
-      <c r="O15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" t="s">
         <v>161</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>162</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
         <v>163</v>
       </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>164</v>
       </c>
-      <c r="H16" t="s">
-        <v>165</v>
-      </c>
       <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" t="s">
         <v>166</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>167</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
         <v>168</v>
       </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>169</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>170</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" t="s">
         <v>171</v>
       </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>19</v>
-      </c>
       <c r="L17" t="s">
+        <v>169</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
         <v>172</v>
       </c>
-      <c r="M17" t="s">
-        <v>170</v>
-      </c>
-      <c r="O17" t="s">
-        <v>19</v>
-      </c>
       <c r="P17" t="s">
+        <v>169</v>
+      </c>
+      <c r="R17" t="s">
+        <v>18</v>
+      </c>
+      <c r="S17" t="s">
         <v>173</v>
       </c>
-      <c r="Q17" t="s">
-        <v>170</v>
-      </c>
-      <c r="S17" t="s">
-        <v>19</v>
-      </c>
       <c r="T17" t="s">
+        <v>169</v>
+      </c>
+      <c r="U17" t="s">
         <v>174</v>
       </c>
-      <c r="U17" t="s">
-        <v>170</v>
-      </c>
       <c r="V17" t="s">
-        <v>175</v>
-      </c>
-      <c r="W17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" t="s">
+        <v>180</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>286</v>
       </c>
-      <c r="C18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" t="s">
-        <v>180</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="C19" t="s">
         <v>181</v>
       </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>182</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>183</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
         <v>184</v>
       </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>304</v>
+      </c>
+      <c r="I19" t="s">
         <v>185</v>
       </c>
-      <c r="H19" t="s">
-        <v>305</v>
-      </c>
-      <c r="I19" t="s">
-        <v>186</v>
-      </c>
       <c r="J19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" t="s">
         <v>187</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>188</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
         <v>189</v>
       </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>190</v>
-      </c>
       <c r="H20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" t="s">
         <v>191</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>192</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>193</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>194</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>296</v>
+      </c>
+      <c r="I21" t="s">
         <v>195</v>
       </c>
-      <c r="H21" t="s">
-        <v>297</v>
-      </c>
-      <c r="I21" t="s">
-        <v>196</v>
-      </c>
       <c r="J21" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="s">
         <v>197</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>198</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>193</v>
+      </c>
+      <c r="G22" t="s">
         <v>199</v>
       </c>
-      <c r="F22" t="s">
-        <v>194</v>
-      </c>
-      <c r="G22" t="s">
-        <v>200</v>
-      </c>
       <c r="H22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s">
         <v>169</v>
@@ -2668,167 +2628,190 @@
         <v>170</v>
       </c>
       <c r="N22" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="O22" t="s">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="P22" t="s">
+        <v>172</v>
+      </c>
+      <c r="R22" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" t="s">
         <v>173</v>
       </c>
-      <c r="Q22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
-      </c>
       <c r="T22" t="s">
+        <v>169</v>
+      </c>
+      <c r="U22" t="s">
         <v>174</v>
       </c>
-      <c r="U22" t="s">
-        <v>170</v>
-      </c>
       <c r="V22" t="s">
-        <v>175</v>
-      </c>
-      <c r="W22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" t="s">
         <v>201</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>202</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G23" t="s">
         <v>203</v>
       </c>
-      <c r="F23" t="s">
-        <v>194</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>204</v>
       </c>
-      <c r="H23" t="s">
-        <v>205</v>
-      </c>
       <c r="J23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" t="s">
         <v>206</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>207</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>208</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" t="s">
+        <v>300</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s">
         <v>209</v>
       </c>
-      <c r="G24" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="L24" t="s">
+        <v>300</v>
+      </c>
+      <c r="N24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" t="s">
+        <v>125</v>
+      </c>
+      <c r="P24" t="s">
         <v>301</v>
       </c>
-      <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="R24" t="s">
+        <v>18</v>
+      </c>
+      <c r="S24" t="s">
+        <v>136</v>
+      </c>
+      <c r="T24" t="s">
+        <v>300</v>
+      </c>
+      <c r="V24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W24" t="s">
         <v>210</v>
       </c>
-      <c r="M24" t="s">
-        <v>301</v>
-      </c>
-      <c r="O24" t="s">
-        <v>19</v>
-      </c>
-      <c r="P24" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q24" t="s">
+      <c r="X24" t="s">
         <v>302</v>
       </c>
-      <c r="S24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T24" t="s">
-        <v>137</v>
-      </c>
-      <c r="U24" t="s">
-        <v>301</v>
-      </c>
-      <c r="W24" t="s">
-        <v>19</v>
-      </c>
-      <c r="X24" t="s">
+      <c r="Z24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="s">
         <v>211</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AB24" t="s">
+        <v>302</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF24" t="s">
         <v>303</v>
       </c>
-      <c r="AA24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>212</v>
-      </c>
-      <c r="AC24" t="s">
+      <c r="AH24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ24" t="s">
         <v>303</v>
       </c>
-      <c r="AE24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>304</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ24" t="s">
+      <c r="AL24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="s">
         <v>214</v>
       </c>
-      <c r="AK24" t="s">
-        <v>304</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>19</v>
-      </c>
       <c r="AN24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>304</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>18</v>
+        <v>303</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" t="s">
+        <v>313</v>
+      </c>
+      <c r="E25" t="s">
+        <v>312</v>
+      </c>
+      <c r="F25" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" t="s">
+        <v>314</v>
+      </c>
+      <c r="H25" t="s">
+        <v>315</v>
+      </c>
+      <c r="I25" t="s">
+        <v>316</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2848,357 +2831,357 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
@@ -3212,35 +3195,35 @@
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>0</v>
@@ -3254,21 +3237,21 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>0</v>
@@ -3282,35 +3265,35 @@
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>0</v>
@@ -3324,35 +3307,35 @@
     </row>
     <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>0</v>
@@ -3366,35 +3349,35 @@
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>0</v>
@@ -3408,21 +3391,21 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>0</v>
@@ -3434,21 +3417,21 @@
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>0</v>
@@ -3462,21 +3445,21 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>0</v>
@@ -3490,59 +3473,59 @@
     </row>
     <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>0</v>
@@ -3551,24 +3534,24 @@
         <v>21</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>0</v>
@@ -3577,36 +3560,36 @@
         <v>15</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>0</v>
@@ -3615,24 +3598,24 @@
         <v>16</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>0</v>
@@ -3641,24 +3624,24 @@
         <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>0</v>
@@ -3667,7 +3650,7 @@
         <v>24</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
